--- a/data/trans_dic/P6901-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,39; 85,88</t>
+          <t>67,45; 85,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,91; 82,82</t>
+          <t>63,18; 83,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,65; 84,5</t>
+          <t>59,74; 84,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,2; 86,48</t>
+          <t>65,83; 86,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,95; 91,59</t>
+          <t>63,13; 91,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,25; 97,05</t>
+          <t>71,36; 96,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,07; 94,65</t>
+          <t>67,93; 94,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,2; 88,68</t>
+          <t>68,11; 87,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,23; 85,36</t>
+          <t>69,84; 85,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,1; 84,91</t>
+          <t>69,27; 85,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,7; 85,63</t>
+          <t>67,49; 86,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,17; 85,18</t>
+          <t>70,92; 85,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,81; 77,98</t>
+          <t>63,49; 78,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,99; 84,25</t>
+          <t>64,89; 84,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,46; 83,63</t>
+          <t>64,84; 83,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 80,62</t>
+          <t>63,02; 80,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,71; 86,88</t>
+          <t>64,34; 87,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,49; 89,52</t>
+          <t>67,35; 88,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,21; 97,41</t>
+          <t>79,09; 98,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,11; 85,75</t>
+          <t>71,91; 85,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,05; 78,62</t>
+          <t>65,68; 77,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,2; 83,78</t>
+          <t>70,7; 83,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,98; 86,66</t>
+          <t>72,66; 86,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,63; 79,98</t>
+          <t>69,24; 80,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,95; 84,36</t>
+          <t>68,76; 84,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,58; 82,57</t>
+          <t>61,52; 83,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,0; 86,86</t>
+          <t>71,65; 87,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,41; 85,27</t>
+          <t>60,47; 84,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,42; 94,17</t>
+          <t>74,32; 93,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,29; 85,15</t>
+          <t>59,66; 85,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,42; 92,55</t>
+          <t>74,93; 93,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,84; 94,2</t>
+          <t>69,24; 94,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73,02; 85,56</t>
+          <t>72,43; 85,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,47; 80,47</t>
+          <t>65,39; 81,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,39; 87,56</t>
+          <t>75,38; 87,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,44; 90,41</t>
+          <t>69,46; 90,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,71; 82,36</t>
+          <t>67,88; 82,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,91; 83,24</t>
+          <t>61,2; 82,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,48; 78,5</t>
+          <t>57,23; 77,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,09; 78,94</t>
+          <t>60,28; 79,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,01; 82,68</t>
+          <t>63,09; 81,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,63; 84,01</t>
+          <t>61,05; 83,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,49; 87,87</t>
+          <t>67,54; 88,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,11; 80,05</t>
+          <t>58,7; 79,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,03; 80,31</t>
+          <t>69,09; 80,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 80,49</t>
+          <t>65,37; 80,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,41; 79,5</t>
+          <t>65,54; 80,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,91; 76,46</t>
+          <t>62,39; 76,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,83; 78,8</t>
+          <t>71,04; 78,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,29; 79,44</t>
+          <t>69,39; 79,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,64; 79,32</t>
+          <t>69,38; 78,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,51; 77,89</t>
+          <t>67,47; 77,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,08</t>
+          <t>71,9; 83,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,79; 83,76</t>
+          <t>71,63; 83,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,06; 88,9</t>
+          <t>79,65; 89,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,4; 84,1</t>
+          <t>72,53; 84,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,42; 79,35</t>
+          <t>72,43; 78,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,98; 79,67</t>
+          <t>71,76; 79,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74,75; 82,01</t>
+          <t>74,66; 81,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,84; 79,81</t>
+          <t>71,71; 79,64</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52670; 68133</t>
+          <t>53505; 68110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48844; 64301</t>
+          <t>49053; 64593</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32613; 46201</t>
+          <t>32663; 46187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46435; 61589</t>
+          <t>46884; 61685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20618; 29530</t>
+          <t>20353; 29434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25823; 34213</t>
+          <t>25158; 34194</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20363; 28314</t>
+          <t>20323; 28325</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37838; 48490</t>
+          <t>37244; 48050</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78355; 95235</t>
+          <t>77919; 95391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78017; 95860</t>
+          <t>78209; 96650</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56420; 72431</t>
+          <t>57084; 72999</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88337; 107239</t>
+          <t>89292; 107047</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93151; 113839</t>
+          <t>92688; 114054</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61341; 78311</t>
+          <t>60319; 78310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63483; 81111</t>
+          <t>62885; 81363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69880; 90279</t>
+          <t>70576; 90293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34163; 45871</t>
+          <t>33971; 46007</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41390; 54903</t>
+          <t>41308; 54298</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44003; 54114</t>
+          <t>43938; 54457</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71191; 84656</t>
+          <t>70997; 84712</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131284; 156270</t>
+          <t>130567; 154974</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108300; 129264</t>
+          <t>109082; 129400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111323; 132181</t>
+          <t>110831; 131977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>144611; 168520</t>
+          <t>145906; 169936</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73605; 92749</t>
+          <t>75594; 93390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48994; 65693</t>
+          <t>48942; 66449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79156; 95490</t>
+          <t>78764; 95702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33946; 47136</t>
+          <t>33426; 46841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34630; 43822</t>
+          <t>34582; 43723</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32469; 45111</t>
+          <t>31605; 45068</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48835; 59926</t>
+          <t>48516; 60431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66711; 91291</t>
+          <t>67098; 91943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114255; 133889</t>
+          <t>113336; 134283</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85443; 106658</t>
+          <t>86666; 108090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131697; 152946</t>
+          <t>131674; 152994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>105678; 137593</t>
+          <t>105707; 138210</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94164; 112869</t>
+          <t>93033; 113093</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49468; 64433</t>
+          <t>47371; 63777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50815; 69405</t>
+          <t>50599; 68103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59700; 79750</t>
+          <t>60903; 80166</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55792; 73217</t>
+          <t>55870; 72532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38863; 53846</t>
+          <t>39128; 53725</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44598; 58064</t>
+          <t>44634; 58242</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61416; 83169</t>
+          <t>60991; 82773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>155742; 181171</t>
+          <t>155863; 181598</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92795; 113896</t>
+          <t>92497; 114546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99506; 122819</t>
+          <t>101257; 124512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>128926; 156689</t>
+          <t>127849; 157713</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>334550; 372165</t>
+          <t>335509; 372213</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>226963; 260196</t>
+          <t>227282; 259495</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>243733; 277615</t>
+          <t>242826; 274945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229201; 264426</t>
+          <t>229067; 262543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>158216; 182869</t>
+          <t>158264; 183829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>153383; 178952</t>
+          <t>153048; 177544</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171011; 192299</t>
+          <t>172284; 193490</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>256445; 297888</t>
+          <t>256929; 297664</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>501482; 549421</t>
+          <t>501537; 546815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>389548; 431185</t>
+          <t>388400; 429377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>423295; 464402</t>
+          <t>422810; 463700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>498342; 553674</t>
+          <t>497433; 552447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6901-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,45; 85,86</t>
+          <t>66,18; 86,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,18; 83,19</t>
+          <t>63,04; 83,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,74; 84,48</t>
+          <t>59,39; 83,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 86,62</t>
+          <t>64,83; 86,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,13; 91,29</t>
+          <t>64,09; 91,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,36; 96,99</t>
+          <t>71,36; 96,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,93; 94,69</t>
+          <t>65,53; 93,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,11; 87,87</t>
+          <t>70,7; 87,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69,84; 85,5</t>
+          <t>69,93; 85,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,27; 85,61</t>
+          <t>70,48; 86,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,49; 86,3</t>
+          <t>66,19; 85,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,92; 85,03</t>
+          <t>70,01; 84,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,49; 78,13</t>
+          <t>63,15; 78,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,89; 84,25</t>
+          <t>65,93; 83,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,84; 83,89</t>
+          <t>63,5; 83,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,02; 80,63</t>
+          <t>65,94; 82,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,34; 87,14</t>
+          <t>64,87; 86,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,35; 88,53</t>
+          <t>67,0; 89,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,09; 98,03</t>
+          <t>79,23; 97,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,91; 85,8</t>
+          <t>72,61; 86,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,68; 77,96</t>
+          <t>65,1; 78,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,7; 83,87</t>
+          <t>69,99; 84,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,66; 86,52</t>
+          <t>72,83; 86,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,24; 80,65</t>
+          <t>71,3; 81,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,76; 84,94</t>
+          <t>67,42; 84,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,52; 83,52</t>
+          <t>61,45; 83,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,65; 87,05</t>
+          <t>71,97; 86,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,47; 84,74</t>
+          <t>66,29; 87,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,32; 93,96</t>
+          <t>72,5; 93,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,66; 85,07</t>
+          <t>59,85; 84,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,93; 93,33</t>
+          <t>74,38; 93,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,24; 94,88</t>
+          <t>62,38; 82,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,43; 85,82</t>
+          <t>72,76; 86,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,39; 81,56</t>
+          <t>64,1; 80,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,38; 87,58</t>
+          <t>76,23; 87,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,46; 90,82</t>
+          <t>69,28; 83,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,88; 82,52</t>
+          <t>67,8; 82,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,2; 82,4</t>
+          <t>63,19; 82,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,23; 77,03</t>
+          <t>56,75; 77,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,28; 79,35</t>
+          <t>60,76; 80,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,09; 81,91</t>
+          <t>63,65; 82,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,05; 83,82</t>
+          <t>61,32; 84,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,54; 88,14</t>
+          <t>67,21; 87,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,7; 79,67</t>
+          <t>68,37; 82,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,09; 80,5</t>
+          <t>68,71; 80,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,37; 80,95</t>
+          <t>66,41; 81,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,54; 80,59</t>
+          <t>64,99; 80,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,39; 76,96</t>
+          <t>67,84; 79,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,81</t>
+          <t>70,82; 79,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,39; 79,22</t>
+          <t>69,03; 78,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,38; 78,56</t>
+          <t>69,24; 79,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,47; 77,33</t>
+          <t>69,95; 79,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,9; 83,51</t>
+          <t>72,29; 83,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,63; 83,1</t>
+          <t>70,59; 83,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,65; 89,46</t>
+          <t>79,3; 89,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,53; 84,03</t>
+          <t>73,44; 81,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,43; 78,97</t>
+          <t>72,44; 79,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 79,34</t>
+          <t>71,93; 79,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74,66; 81,88</t>
+          <t>75,14; 82,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,71; 79,64</t>
+          <t>72,95; 79,26</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54864</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98599</t>
+          <t>105407</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53505; 68110</t>
+          <t>52503; 68319</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49053; 64593</t>
+          <t>48946; 64486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32663; 46187</t>
+          <t>32471; 45828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46884; 61685</t>
+          <t>48652; 64558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20353; 29434</t>
+          <t>20664; 29562</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25158; 34194</t>
+          <t>25157; 34178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20323; 28325</t>
+          <t>19604; 28116</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37244; 48050</t>
+          <t>42291; 52604</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77919; 95391</t>
+          <t>78020; 95063</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78209; 96650</t>
+          <t>79568; 97192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57084; 72999</t>
+          <t>55993; 71967</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89292; 107047</t>
+          <t>94422; 113687</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80382</t>
+          <t>99253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78454</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>158835</t>
+          <t>184950</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92688; 114054</t>
+          <t>92185; 114719</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60319; 78310</t>
+          <t>61287; 78052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62885; 81363</t>
+          <t>61580; 81086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70576; 90293</t>
+          <t>87693; 110320</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33971; 46007</t>
+          <t>34251; 45759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41308; 54298</t>
+          <t>41094; 54837</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43938; 54457</t>
+          <t>44013; 53900</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70997; 84712</t>
+          <t>78023; 92615</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130567; 154974</t>
+          <t>129404; 155945</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109082; 129400</t>
+          <t>107988; 130087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110831; 131977</t>
+          <t>111092; 131884</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>145906; 169936</t>
+          <t>171447; 196455</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41066</t>
+          <t>54382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79887</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>106686</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75594; 93390</t>
+          <t>74125; 93234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48942; 66449</t>
+          <t>48890; 66041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78764; 95702</t>
+          <t>79116; 95320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33426; 46841</t>
+          <t>45648; 60235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34582; 43723</t>
+          <t>33736; 43696</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31605; 45068</t>
+          <t>31707; 44960</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48516; 60431</t>
+          <t>48162; 60350</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67098; 91943</t>
+          <t>44111; 58501</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>113336; 134283</t>
+          <t>113849; 134660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86666; 108090</t>
+          <t>84950; 106820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131674; 152994</t>
+          <t>133161; 153228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>105707; 138210</t>
+          <t>96691; 116271</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70665</t>
+          <t>77159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74186</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>144851</t>
+          <t>158985</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93033; 113093</t>
+          <t>92917; 112582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47371; 63777</t>
+          <t>48909; 63824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50599; 68103</t>
+          <t>50175; 68639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60903; 80166</t>
+          <t>65687; 86481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55870; 72532</t>
+          <t>56361; 72970</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39128; 53725</t>
+          <t>39306; 54142</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44634; 58242</t>
+          <t>44413; 58136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60991; 82773</t>
+          <t>73388; 88843</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>155863; 181598</t>
+          <t>155007; 181389</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92497; 114546</t>
+          <t>93975; 114782</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101257; 124512</t>
+          <t>100401; 124135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>127849; 157713</t>
+          <t>146170; 171443</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246977</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>276261</t>
+          <t>267835</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>523238</t>
+          <t>556030</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>335509; 372213</t>
+          <t>334494; 373635</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>227282; 259495</t>
+          <t>226127; 258741</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242826; 274945</t>
+          <t>242356; 277379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229067; 262543</t>
+          <t>269317; 304522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>158264; 183829</t>
+          <t>159126; 183386</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>153048; 177544</t>
+          <t>150830; 178059</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>172284; 193490</t>
+          <t>171528; 194382</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>256929; 297664</t>
+          <t>253612; 280893</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>501537; 546815</t>
+          <t>501604; 547366</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>388400; 429377</t>
+          <t>389279; 428998</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>422810; 463700</t>
+          <t>425538; 464599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>497433; 552447</t>
+          <t>532766; 578889</t>
         </is>
       </c>
     </row>
